--- a/output/Гонконг 25.08.2026 (обработка).xlsx
+++ b/output/Гонконг 25.08.2026 (обработка).xlsx
@@ -521,6 +521,15 @@
     <col width="15.88" customWidth="1" min="4" max="4"/>
     <col width="17.63" customWidth="1" min="5" max="5"/>
     <col width="14.63" customWidth="1" min="6" max="6"/>
+    <col width="14.63" customWidth="1" min="7" max="7"/>
+    <col width="12.6328125" customWidth="1" min="8" max="8"/>
+    <col width="12.6328125" customWidth="1" min="9" max="9"/>
+    <col width="12.6328125" customWidth="1" min="10" max="10"/>
+    <col width="12.6328125" customWidth="1" min="11" max="11"/>
+    <col width="12.6328125" customWidth="1" min="12" max="12"/>
+    <col width="12.6328125" customWidth="1" min="13" max="13"/>
+    <col width="12.6328125" customWidth="1" min="14" max="14"/>
+    <col width="12.6328125" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="32.25" customHeight="1">
@@ -738,7 +747,9 @@
       <c r="D4" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E4" s="9" t="n"/>
+      <c r="E4" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="F4" s="9" t="n">
         <v>1</v>
       </c>
@@ -851,7 +862,10 @@
         <v/>
       </c>
       <c r="D6" s="15" t="n"/>
-      <c r="E6" s="15" t="n"/>
+      <c r="E6" s="15">
+        <f>E4</f>
+        <v/>
+      </c>
       <c r="F6" s="15">
         <f>F4</f>
         <v/>
@@ -929,7 +943,10 @@
         <v/>
       </c>
       <c r="D8" s="15" t="n"/>
-      <c r="E8" s="15" t="n"/>
+      <c r="E8" s="15">
+        <f>E4</f>
+        <v/>
+      </c>
       <c r="F8" s="15" t="n"/>
       <c r="G8" s="15">
         <f>G4</f>
@@ -1007,7 +1024,10 @@
         <v/>
       </c>
       <c r="D10" s="15" t="n"/>
-      <c r="E10" s="15" t="n"/>
+      <c r="E10" s="15">
+        <f>E4</f>
+        <v/>
+      </c>
       <c r="F10" s="15">
         <f>F4</f>
         <v/>

--- a/output/Гонконг 25.08.2026 (обработка).xlsx
+++ b/output/Гонконг 25.08.2026 (обработка).xlsx
@@ -522,14 +522,14 @@
     <col width="17.63" customWidth="1" min="5" max="5"/>
     <col width="14.63" customWidth="1" min="6" max="6"/>
     <col width="14.63" customWidth="1" min="7" max="7"/>
-    <col width="12.6328125" customWidth="1" min="8" max="8"/>
-    <col width="12.6328125" customWidth="1" min="9" max="9"/>
-    <col width="12.6328125" customWidth="1" min="10" max="10"/>
-    <col width="12.6328125" customWidth="1" min="11" max="11"/>
-    <col width="12.6328125" customWidth="1" min="12" max="12"/>
-    <col width="12.6328125" customWidth="1" min="13" max="13"/>
-    <col width="12.6328125" customWidth="1" min="14" max="14"/>
-    <col width="12.6328125" customWidth="1" min="15" max="15"/>
+    <col width="14.63" customWidth="1" min="8" max="8"/>
+    <col width="14.63" customWidth="1" min="9" max="9"/>
+    <col width="15.5" customWidth="1" min="10" max="10"/>
+    <col width="16.13" customWidth="1" min="11" max="11"/>
+    <col width="14.63" customWidth="1" min="12" max="12"/>
+    <col width="14.63" customWidth="1" min="13" max="13"/>
+    <col width="14.63" customWidth="1" min="14" max="14"/>
+    <col width="14.63" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="32.25" customHeight="1">
